--- a/output/pdf_financials_xlsx/SUI.xlsx
+++ b/output/pdf_financials_xlsx/SUI.xlsx
@@ -6149,31 +6149,31 @@
         <v>1.968612</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>2.296331</v>
+        <v>2.020922</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.778685</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.949296</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.361912</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.406452</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.420943</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.350883</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.08612</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.027296</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>0</v>
@@ -7817,22 +7817,22 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.998536</v>
+        <v>0.395467</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.493653</v>
+        <v>0.162832</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.09070400000000001</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.078628</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.027135</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.002763</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>0</v>
@@ -15836,7 +15836,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -16798,7 +16802,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -18263,7 +18271,11 @@
           <t>Reserves (note 8)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -19370,7 +19382,11 @@
           <t>Reserves (note 8)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -20649,7 +20665,11 @@
           <t>Reserves (note 10)</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -25349,7 +25369,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SUI.xlsx
+++ b/output/pdf_financials_xlsx/SUI.xlsx
@@ -1061,16 +1061,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.013103</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000374</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.007501</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>4.1e-05</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -2073,16 +2073,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.85843</v>
+        <v>-4.871533</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.29373</v>
+        <v>-1.294104</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.660971</v>
+        <v>-1.668472</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.470865</v>
+        <v>-1.470906</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.377921</v>
@@ -2197,16 +2197,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.85843</v>
+        <v>-4.871533</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.29373</v>
+        <v>-1.294104</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.660971</v>
+        <v>-1.668472</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.470865</v>
+        <v>-1.470906</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.377921</v>
@@ -2512,37 +2512,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.034794</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.131537</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.10766</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.022614</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.056072</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.006258</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.004922</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.00209</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.00302</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.294556</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.010132</v>
       </c>
       <c r="M34" s="1" t="inlineStr">
         <is>
@@ -2550,19 +2550,19 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.000339</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.130192</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.127154</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.005538</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.005538</v>
       </c>
     </row>
     <row r="35">
@@ -2632,37 +2632,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.034794</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.131537</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.10766</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.022614</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.056072</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.006258</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.004922</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.00209</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.00302</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.294556</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.010132</v>
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
@@ -2670,19 +2670,19 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.000339</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.130192</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.127154</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.005538</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.005538</v>
       </c>
     </row>
     <row r="37">
@@ -3352,37 +3352,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.034794</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.143863</v>
+        <v>0.012326</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.123204</v>
+        <v>0.015544</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.038133</v>
+        <v>0.015519</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.058314</v>
+        <v>0.002242</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.011422</v>
+        <v>0.005164</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.007153</v>
+        <v>0.002231</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.00209</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.00302</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.294556</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.010307</v>
+        <v>0.000175</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -3390,19 +3390,19 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.000339</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.153997</v>
+        <v>0.023805</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.141554</v>
+        <v>0.0144</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.005538</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.005538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -17113,7 +17113,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -53468,7 +53468,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E443" s="5" t="n">
